--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2594" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T15:37:21+00:00</t>
+    <t>2026-03-27T15:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
   </si>
   <si>
     <t>Extension du modèle EHDSPatient pour le contexte français.
-Traduit en français les libellés des éléments hérités et ajoute des champs spécifiques au système de santé français.</t>
+Traduit en français les libellés des éléments hérités (deux approches testées) et ajoute des champs spécifiques au système de santé français.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -261,10 +261,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant du patient</t>
-  </si>
-  <si>
-    <t>Identifiant unique du patient dans un périmètre défini (par ex. identifiant national de santé, ou identifiant temporaire du DPI).</t>
+    <t>An identifier of the patient that is unique within a defined scope (typically a national patient identifier, but it can also be a temporary identifier issued by the EHR).</t>
   </si>
   <si>
     <t>EHDSPatient.identifier</t>
@@ -309,10 +306,7 @@
 dateTime</t>
   </si>
   <si>
-    <t>Patient décédé / Date de décès</t>
-  </si>
-  <si>
-    <t>Indique si le patient est décédé ou renseigne la date de décès.</t>
+    <t>Whether the patient is deceased or date of death.</t>
   </si>
   <si>
     <t>EHDSPatient.deceased[x]</t>
@@ -347,10 +341,7 @@
 </t>
   </si>
   <si>
-    <t>Adresse(s)</t>
-  </si>
-  <si>
-    <t>Adresses postale et personnelle/professionnelle du patient.</t>
+    <t>The addresses are always sequences of address parts (e.g. street address line, country, postal code, city) even if postal address formats may vary depending on the country. An address may or may not include a specific use code; if this attribute is not present it is assumed to be the default address useful for any purpose.</t>
   </si>
   <si>
     <t>EHDSPatient.address</t>
@@ -363,10 +354,7 @@
 </t>
   </si>
   <si>
-    <t>Coordonnées de contact</t>
-  </si>
-  <si>
-    <t>Informations de contact du patient (téléphone, email, etc.).</t>
+    <t>Contact information.</t>
   </si>
   <si>
     <t>EHDSPatient.telecom</t>
@@ -1730,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
@@ -1738,7 +1726,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
@@ -1754,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
@@ -1814,7 +1802,7 @@
         <v>22</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35">
@@ -1842,7 +1830,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39">
@@ -1850,7 +1838,7 @@
         <v>30</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -1858,7 +1846,7 @@
         <v>31</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
@@ -1874,15 +1862,15 @@
         <v>35</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
@@ -1898,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46">
@@ -1906,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47">
@@ -1922,7 +1910,7 @@
         <v>8</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49">
@@ -1930,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50">
@@ -1984,7 +1972,7 @@
         <v>22</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
@@ -2012,7 +2000,7 @@
         <v>28</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61">
@@ -2020,7 +2008,7 @@
         <v>30</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62">
@@ -2028,7 +2016,7 @@
         <v>31</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63">
@@ -2044,7 +2032,7 @@
         <v>35</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2343,11 +2331,9 @@
       <c r="L3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="M3" s="2"/>
+      <c r="N3" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -2398,7 +2384,7 @@
         <v>73</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>79</v>
@@ -2418,10 +2404,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
@@ -2444,13 +2430,13 @@
         <v>73</v>
       </c>
       <c r="L4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M4" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -2501,7 +2487,7 @@
         <v>73</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>74</v>
@@ -2521,10 +2507,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
@@ -2547,13 +2533,13 @@
         <v>73</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -2604,7 +2590,7 @@
         <v>73</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>74</v>
@@ -2624,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
@@ -2650,13 +2636,13 @@
         <v>73</v>
       </c>
       <c r="L6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M6" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="N6" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -2707,7 +2693,7 @@
         <v>73</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>74</v>
@@ -2727,10 +2713,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
@@ -2753,13 +2739,13 @@
         <v>73</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -2786,31 +2772,31 @@
         <v>73</v>
       </c>
       <c r="Y7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG7" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="Z7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AA7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>74</v>
@@ -2830,10 +2816,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2856,13 +2842,11 @@
         <v>73</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="M8" s="2"/>
       <c r="N8" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -2913,7 +2897,7 @@
         <v>73</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>74</v>
@@ -2933,10 +2917,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -2959,13 +2943,11 @@
         <v>73</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="M9" s="2"/>
       <c r="N9" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -3016,7 +2998,7 @@
         <v>73</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>74</v>
@@ -3036,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -3065,10 +3047,10 @@
         <v>80</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -3119,7 +3101,7 @@
         <v>73</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>74</v>
@@ -3139,10 +3121,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -3168,10 +3150,10 @@
         <v>80</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -3222,7 +3204,7 @@
         <v>73</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>74</v>
@@ -3242,10 +3224,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3268,13 +3250,13 @@
         <v>73</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -3325,7 +3307,7 @@
         <v>73</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>74</v>
@@ -3345,10 +3327,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -3371,13 +3353,13 @@
         <v>73</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -3428,7 +3410,7 @@
         <v>73</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>74</v>
@@ -3448,10 +3430,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -3474,13 +3456,13 @@
         <v>73</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -3531,7 +3513,7 @@
         <v>73</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>74</v>
@@ -3548,13 +3530,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="C15" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3580,10 +3562,10 @@
         <v>76</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -3634,7 +3616,7 @@
         <v>73</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>74</v>
@@ -3646,18 +3628,18 @@
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3680,13 +3662,13 @@
         <v>73</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -3737,7 +3719,7 @@
         <v>73</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>74</v>
@@ -3746,7 +3728,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>73</v>
@@ -3754,13 +3736,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3783,13 +3765,13 @@
         <v>73</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -3828,19 +3810,19 @@
         <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AE17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>74</v>
@@ -3852,18 +3834,18 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3886,16 +3868,16 @@
         <v>73</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -3903,7 +3885,7 @@
       </c>
       <c r="R18" s="2"/>
       <c r="S18" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>73</v>
@@ -3945,7 +3927,7 @@
         <v>73</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -3962,13 +3944,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -3991,13 +3973,13 @@
         <v>73</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -4024,11 +4006,11 @@
         <v>73</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z19" s="2"/>
       <c r="AA19" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AB19" t="s" s="2">
         <v>73</v>
@@ -4046,7 +4028,7 @@
         <v>73</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>74</v>
@@ -4055,25 +4037,25 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" t="s" s="2">
@@ -4095,10 +4077,10 @@
         <v>76</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -4149,7 +4131,7 @@
         <v>73</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>74</v>
@@ -4161,18 +4143,18 @@
         <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4192,19 +4174,19 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
@@ -4254,7 +4236,7 @@
         <v>73</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>74</v>
@@ -4271,13 +4253,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4297,16 +4279,16 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -4357,7 +4339,7 @@
         <v>73</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>74</v>
@@ -4369,18 +4351,18 @@
         <v>73</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4397,22 +4379,22 @@
         <v>73</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
@@ -4462,7 +4444,7 @@
         <v>73</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>74</v>
@@ -4474,18 +4456,18 @@
         <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4508,16 +4490,16 @@
         <v>73</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
@@ -4543,13 +4525,13 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>73</v>
@@ -4567,7 +4549,7 @@
         <v>73</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>74</v>
@@ -4579,22 +4561,22 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -4613,16 +4595,16 @@
         <v>73</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
@@ -4672,7 +4654,7 @@
         <v>73</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>74</v>
@@ -4681,25 +4663,25 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
@@ -4718,16 +4700,16 @@
         <v>73</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
@@ -4777,7 +4759,7 @@
         <v>73</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>74</v>
@@ -4786,7 +4768,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>73</v>
@@ -4794,13 +4776,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4823,13 +4805,13 @@
         <v>73</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -4868,17 +4850,17 @@
         <v>73</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AD27" s="2"/>
       <c r="AE27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>74</v>
@@ -4890,21 +4872,21 @@
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>73</v>
@@ -4917,7 +4899,7 @@
         <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>73</v>
@@ -4926,13 +4908,13 @@
         <v>73</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -4983,7 +4965,7 @@
         <v>73</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>74</v>
@@ -4995,22 +4977,22 @@
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -5023,25 +5005,25 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Q29" t="s" s="2">
         <v>73</v>
@@ -5090,7 +5072,7 @@
         <v>73</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>74</v>
@@ -5102,18 +5084,18 @@
         <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5133,20 +5115,20 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>73</v>
@@ -5183,19 +5165,19 @@
         <v>73</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AE30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>74</v>
@@ -5207,21 +5189,21 @@
         <v>73</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E31" t="s" s="2">
         <v>73</v>
@@ -5234,26 +5216,26 @@
         <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q31" t="s" s="2">
         <v>73</v>
@@ -5302,7 +5284,7 @@
         <v>73</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>74</v>
@@ -5314,18 +5296,18 @@
         <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5348,13 +5330,13 @@
         <v>73</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -5405,7 +5387,7 @@
         <v>73</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>74</v>
@@ -5414,7 +5396,7 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>73</v>
@@ -5422,17 +5404,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
@@ -5451,16 +5433,16 @@
         <v>73</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -5498,19 +5480,19 @@
         <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AE33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>74</v>
@@ -5522,18 +5504,18 @@
         <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5550,25 +5532,25 @@
         <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="Q34" t="s" s="2">
         <v>73</v>
@@ -5593,13 +5575,13 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AB34" t="s" s="2">
         <v>73</v>
@@ -5617,7 +5599,7 @@
         <v>73</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>74</v>
@@ -5629,18 +5611,18 @@
         <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5660,22 +5642,22 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="Q35" t="s" s="2">
         <v>73</v>
@@ -5700,13 +5682,13 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AB35" t="s" s="2">
         <v>73</v>
@@ -5724,7 +5706,7 @@
         <v>73</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
@@ -5736,18 +5718,18 @@
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5767,22 +5749,22 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Q36" t="s" s="2">
         <v>73</v>
@@ -5792,10 +5774,10 @@
         <v>73</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="V36" t="s" s="2">
         <v>73</v>
@@ -5831,7 +5813,7 @@
         <v>73</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>74</v>
@@ -5843,18 +5825,18 @@
         <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5874,19 +5856,19 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
@@ -5900,7 +5882,7 @@
         <v>73</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="V37" t="s" s="2">
         <v>73</v>
@@ -5936,7 +5918,7 @@
         <v>73</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>74</v>
@@ -5945,21 +5927,21 @@
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5979,16 +5961,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6039,7 +6021,7 @@
         <v>73</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
@@ -6051,18 +6033,18 @@
         <v>73</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6082,19 +6064,19 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
@@ -6144,7 +6126,7 @@
         <v>73</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>74</v>
@@ -6156,18 +6138,18 @@
         <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6184,32 +6166,32 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P40" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="Q40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R40" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Q40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="R40" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="S40" t="s" s="2">
         <v>73</v>
       </c>
@@ -6253,7 +6235,7 @@
         <v>73</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>74</v>
@@ -6265,18 +6247,18 @@
         <v>73</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6296,22 +6278,22 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P41" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="Q41" t="s" s="2">
         <v>73</v>
@@ -6360,7 +6342,7 @@
         <v>73</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
@@ -6372,18 +6354,18 @@
         <v>73</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6403,22 +6385,22 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P42" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="Q42" t="s" s="2">
         <v>73</v>
@@ -6467,7 +6449,7 @@
         <v>73</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>
@@ -6479,18 +6461,18 @@
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6510,22 +6492,22 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P43" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Q43" t="s" s="2">
         <v>73</v>
@@ -6550,11 +6532,11 @@
         <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z43" s="2"/>
       <c r="AA43" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AB43" t="s" s="2">
         <v>73</v>
@@ -6572,7 +6554,7 @@
         <v>73</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>74</v>
@@ -6584,18 +6566,18 @@
         <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6615,22 +6597,22 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="P44" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>73</v>
@@ -6679,7 +6661,7 @@
         <v>73</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>74</v>
@@ -6691,18 +6673,18 @@
         <v>73</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6719,25 +6701,25 @@
         <v>73</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>73</v>
@@ -6786,7 +6768,7 @@
         <v>73</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>74</v>
@@ -6798,18 +6780,18 @@
         <v>73</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6829,22 +6811,22 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P46" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>73</v>
@@ -6893,7 +6875,7 @@
         <v>73</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>74</v>
@@ -6905,18 +6887,18 @@
         <v>73</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6939,17 +6921,17 @@
         <v>73</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>73</v>
@@ -6974,13 +6956,13 @@
         <v>73</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>73</v>
@@ -6998,7 +6980,7 @@
         <v>73</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>74</v>
@@ -7010,18 +6992,18 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7044,19 +7026,19 @@
         <v>73</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P48" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>73</v>
@@ -7105,7 +7087,7 @@
         <v>73</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>74</v>
@@ -7117,18 +7099,18 @@
         <v>73</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7151,19 +7133,19 @@
         <v>73</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="P49" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>73</v>
@@ -7212,7 +7194,7 @@
         <v>73</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>74</v>
@@ -7224,18 +7206,18 @@
         <v>73</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7258,19 +7240,19 @@
         <v>73</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="P50" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="Q50" t="s" s="2">
         <v>73</v>
@@ -7319,7 +7301,7 @@
         <v>73</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>74</v>
@@ -7331,18 +7313,18 @@
         <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7365,13 +7347,13 @@
         <v>73</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -7422,7 +7404,7 @@
         <v>73</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>74</v>
@@ -7431,7 +7413,7 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>73</v>
@@ -7439,17 +7421,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
@@ -7468,16 +7450,16 @@
         <v>73</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
@@ -7527,7 +7509,7 @@
         <v>73</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>74</v>
@@ -7539,22 +7521,22 @@
         <v>73</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
@@ -7567,25 +7549,25 @@
         <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>73</v>
@@ -7634,7 +7616,7 @@
         <v>73</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>74</v>
@@ -7646,18 +7628,18 @@
         <v>73</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7680,17 +7662,17 @@
         <v>73</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>73</v>
@@ -7715,13 +7697,13 @@
         <v>73</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AB54" t="s" s="2">
         <v>73</v>
@@ -7739,7 +7721,7 @@
         <v>73</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>74</v>
@@ -7751,18 +7733,18 @@
         <v>73</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7785,17 +7767,17 @@
         <v>73</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>73</v>
@@ -7844,7 +7826,7 @@
         <v>73</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>74</v>
@@ -7853,21 +7835,21 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7890,19 +7872,19 @@
         <v>73</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P56" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>73</v>
@@ -7951,7 +7933,7 @@
         <v>73</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>74</v>
@@ -7960,21 +7942,21 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7997,17 +7979,17 @@
         <v>73</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>73</v>
@@ -8056,7 +8038,7 @@
         <v>73</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>74</v>
@@ -8065,21 +8047,21 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8102,17 +8084,17 @@
         <v>73</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="Q58" t="s" s="2">
         <v>73</v>
@@ -8137,13 +8119,13 @@
         <v>73</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>73</v>
@@ -8161,7 +8143,7 @@
         <v>73</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>74</v>
@@ -8173,18 +8155,18 @@
         <v>73</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8207,17 +8189,17 @@
         <v>73</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>73</v>
@@ -8266,7 +8248,7 @@
         <v>73</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>74</v>
@@ -8275,21 +8257,21 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8312,13 +8294,13 @@
         <v>73</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -8369,7 +8351,7 @@
         <v>73</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>74</v>
@@ -8381,18 +8363,18 @@
         <v>73</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8415,19 +8397,19 @@
         <v>73</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="P61" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="Q61" t="s" s="2">
         <v>73</v>
@@ -8476,7 +8458,7 @@
         <v>73</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>74</v>
@@ -8488,18 +8470,18 @@
         <v>73</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8522,13 +8504,13 @@
         <v>73</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8579,7 +8561,7 @@
         <v>73</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>74</v>
@@ -8588,7 +8570,7 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>73</v>
@@ -8596,17 +8578,17 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" t="s" s="2">
@@ -8625,16 +8607,16 @@
         <v>73</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8684,7 +8666,7 @@
         <v>73</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>74</v>
@@ -8696,22 +8678,22 @@
         <v>73</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" t="s" s="2">
@@ -8724,25 +8706,25 @@
         <v>73</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P64" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>73</v>
@@ -8791,7 +8773,7 @@
         <v>73</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>74</v>
@@ -8803,18 +8785,18 @@
         <v>73</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -8837,19 +8819,19 @@
         <v>73</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>73</v>
@@ -8874,13 +8856,13 @@
         <v>73</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>73</v>
@@ -8898,7 +8880,7 @@
         <v>73</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>79</v>
@@ -8910,18 +8892,18 @@
         <v>73</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -8944,19 +8926,19 @@
         <v>73</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="P66" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>73</v>
@@ -9005,7 +8987,7 @@
         <v>73</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>74</v>
@@ -9017,22 +8999,22 @@
         <v>73</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" t="s" s="2">
@@ -9051,16 +9033,16 @@
         <v>73</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9110,7 +9092,7 @@
         <v>73</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>74</v>
@@ -9122,18 +9104,18 @@
         <v>73</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9153,22 +9135,22 @@
         <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="P68" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="Q68" t="s" s="2">
         <v>73</v>
@@ -9217,7 +9199,7 @@
         <v>73</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>74</v>
@@ -9229,18 +9211,18 @@
         <v>73</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9257,25 +9239,25 @@
         <v>73</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="P69" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>73</v>
@@ -9324,7 +9306,7 @@
         <v>73</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>74</v>
@@ -9336,18 +9318,18 @@
         <v>73</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9370,13 +9352,13 @@
         <v>73</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -9427,7 +9409,7 @@
         <v>73</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>74</v>
@@ -9436,7 +9418,7 @@
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>73</v>
@@ -9444,17 +9426,17 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -9473,16 +9455,16 @@
         <v>73</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9532,7 +9514,7 @@
         <v>73</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>74</v>
@@ -9544,22 +9526,22 @@
         <v>73</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
@@ -9572,25 +9554,25 @@
         <v>73</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="P72" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Q72" t="s" s="2">
         <v>73</v>
@@ -9639,7 +9621,7 @@
         <v>73</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>74</v>
@@ -9651,18 +9633,18 @@
         <v>73</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9682,19 +9664,19 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -9744,7 +9726,7 @@
         <v>73</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>79</v>
@@ -9756,18 +9738,18 @@
         <v>73</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9787,16 +9769,16 @@
         <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -9823,13 +9805,13 @@
         <v>73</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>73</v>
@@ -9847,7 +9829,7 @@
         <v>73</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>79</v>
@@ -9859,7 +9841,7 @@
         <v>73</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
